--- a/artfynd/A 47079-2025 artfynd.xlsx
+++ b/artfynd/A 47079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000729</v>
       </c>
       <c r="B2" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47079-2025 artfynd.xlsx
+++ b/artfynd/A 47079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000729</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47079-2025 artfynd.xlsx
+++ b/artfynd/A 47079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000729</v>
       </c>
       <c r="B2" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47079-2025 artfynd.xlsx
+++ b/artfynd/A 47079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000729</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47079-2025 artfynd.xlsx
+++ b/artfynd/A 47079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000729</v>
       </c>
       <c r="B2" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
